--- a/tests/fixtures/lom/105098-1-LOM.xlsx
+++ b/tests/fixtures/lom/105098-1-LOM.xlsx
@@ -15,20 +15,25 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>QTY</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PART NO</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
@@ -37,42 +42,241 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>105097-1</t>
+          <t>J</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PLATE</t>
+          <t>40002-2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1/4-20NC HHCS X 5/8 L</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>105097-1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>INTERCOM MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>105096-1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CHARGE CABLE BRACKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>105095-1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PLATFORM SWITCH MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>105094-1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PLATFORM REST SUB-WELDMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>104977-1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BATTERY BOX MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>104124-2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CONTROL BOX MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>104124-1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CONTROL BOX MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>103603-1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>MAIN PLATFORM WELDMENT</t>
         </is>
@@ -210,17 +414,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>105097-1</t>
+          <t>40002-2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PLATE</t>
+          <t>1/4-20NC HHCS X 5/8 L</t>
         </is>
       </c>
     </row>
@@ -232,15 +436,169 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>105097-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>INTERCOM MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>105096-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CHARGE CABLE BRACKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>105095-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PLATFORM SWITCH MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>105094-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PLATFORM REST SUB-WELDMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>104977-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BATTERY BOX MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>104124-2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CONTROL BOX MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>104124-1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CONTROL BOX MOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>103603-1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>MAIN PLATFORM WELDMENT</t>
         </is>
